--- a/artfynd/A 4962-2025 artfynd.xlsx
+++ b/artfynd/A 4962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79608703</v>
+        <v>79608786</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Området kring Nordgrenmyran-Risbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612464.8445497694</v>
+        <v>612342</v>
       </c>
       <c r="R2" t="n">
-        <v>7185999.163592672</v>
+        <v>7186035</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,19 +743,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79608786</v>
+        <v>79608840</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612342.1011877119</v>
+        <v>612342</v>
       </c>
       <c r="R3" t="n">
-        <v>7186035.137569707</v>
+        <v>7186034</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +840,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79608723</v>
+        <v>79608702</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,7 +900,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612341.9897584147</v>
+        <v>612695</v>
       </c>
       <c r="R4" t="n">
-        <v>7186038.121968487</v>
+        <v>7185923</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +942,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79608840</v>
+        <v>79608703</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +982,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Området kring Nordgrenmyran-Risbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612342.1489431512</v>
+        <v>612465</v>
       </c>
       <c r="R5" t="n">
-        <v>7186033.858540755</v>
+        <v>7185999</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1094,19 +1044,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,6 +1070,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>79608723</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Området kring Nordgrenmyran-Risbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>612342</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7186038</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-08-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-08-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
